--- a/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
+++ b/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 27/04/2026</t>
+          <t>Generated: 28/04/2026</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18300,7 @@
         <v>45614</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2" s="7" t="b">
         <v>1</v>
@@ -18333,7 +18333,7 @@
         <v>45719</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H3" s="9" t="b">
         <v>1</v>
@@ -18366,7 +18366,7 @@
         <v>45744</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H4" s="7" t="b">
         <v>1</v>
@@ -18399,7 +18399,7 @@
         <v>45772</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H5" s="9" t="b">
         <v>1</v>
@@ -18432,7 +18432,7 @@
         <v>45610</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H6" s="7" t="b">
         <v>1</v>
@@ -18465,7 +18465,7 @@
         <v>45663</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H7" s="9" t="b">
         <v>1</v>
@@ -18498,7 +18498,7 @@
         <v>45672</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H8" s="7" t="b">
         <v>1</v>
@@ -18531,7 +18531,7 @@
         <v>45708</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H9" s="9" t="b">
         <v>1</v>
@@ -18564,7 +18564,7 @@
         <v>45770</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H10" s="7" t="b">
         <v>1</v>
@@ -18597,7 +18597,7 @@
         <v>45784</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H11" s="9" t="b">
         <v>0</v>
@@ -18630,7 +18630,7 @@
         <v>45789</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H12" s="7" t="b">
         <v>0</v>
@@ -18663,7 +18663,7 @@
         <v>45595</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H13" s="9" t="b">
         <v>1</v>
@@ -18696,7 +18696,7 @@
         <v>45602</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H14" s="7" t="b">
         <v>1</v>
@@ -18729,7 +18729,7 @@
         <v>45733</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H15" s="9" t="b">
         <v>1</v>
@@ -18762,7 +18762,7 @@
         <v>45750</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H16" s="7" t="b">
         <v>1</v>
@@ -18795,7 +18795,7 @@
         <v>45775</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H17" s="9" t="b">
         <v>1</v>
@@ -18828,7 +18828,7 @@
         <v>45786</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H18" s="7" t="b">
         <v>0</v>
@@ -18861,7 +18861,7 @@
         <v>45698</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H19" s="9" t="b">
         <v>1</v>
@@ -18894,7 +18894,7 @@
         <v>45763</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H20" s="7" t="b">
         <v>1</v>
@@ -18927,7 +18927,7 @@
         <v>45597</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H21" s="9" t="b">
         <v>1</v>
@@ -18960,7 +18960,7 @@
         <v>45603</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H22" s="7" t="b">
         <v>1</v>
@@ -18993,7 +18993,7 @@
         <v>45616</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H23" s="9" t="b">
         <v>1</v>
@@ -19026,7 +19026,7 @@
         <v>45624</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H24" s="7" t="b">
         <v>1</v>
@@ -19059,7 +19059,7 @@
         <v>45652</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H25" s="9" t="b">
         <v>1</v>
@@ -19092,7 +19092,7 @@
         <v>45679</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H26" s="7" t="b">
         <v>1</v>
@@ -19125,7 +19125,7 @@
         <v>45681</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H27" s="9" t="b">
         <v>1</v>
@@ -19158,7 +19158,7 @@
         <v>45777</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H28" s="7" t="b">
         <v>0</v>
@@ -19191,7 +19191,7 @@
         <v>45793</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H29" s="9" t="b">
         <v>0</v>
@@ -19224,7 +19224,7 @@
         <v>45504</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H30" s="7" t="b">
         <v>1</v>
@@ -19257,7 +19257,7 @@
         <v>45611</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H31" s="9" t="b">
         <v>1</v>
@@ -19290,7 +19290,7 @@
         <v>45651</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H32" s="7" t="b">
         <v>1</v>
@@ -19323,7 +19323,7 @@
         <v>45749</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H33" s="9" t="b">
         <v>1</v>
@@ -19356,7 +19356,7 @@
         <v>45777</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H34" s="7" t="b">
         <v>0</v>
@@ -19389,7 +19389,7 @@
         <v>45806</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H35" s="9" t="b">
         <v>0</v>
@@ -19422,7 +19422,7 @@
         <v>45733</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H36" s="7" t="b">
         <v>1</v>
@@ -19455,7 +19455,7 @@
         <v>45737</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H37" s="9" t="b">
         <v>1</v>
@@ -19488,7 +19488,7 @@
         <v>45768</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H38" s="7" t="b">
         <v>1</v>
@@ -19521,7 +19521,7 @@
         <v>45688</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H39" s="9" t="b">
         <v>1</v>
@@ -19554,7 +19554,7 @@
         <v>45700</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H40" s="7" t="b">
         <v>1</v>
@@ -19587,7 +19587,7 @@
         <v>45715</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H41" s="9" t="b">
         <v>1</v>
@@ -19620,7 +19620,7 @@
         <v>45750</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H42" s="7" t="b">
         <v>1</v>
@@ -19653,7 +19653,7 @@
         <v>45771</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H43" s="9" t="b">
         <v>1</v>
@@ -19686,7 +19686,7 @@
         <v>45771</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H44" s="7" t="b">
         <v>1</v>
@@ -19719,7 +19719,7 @@
         <v>45775</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H45" s="9" t="b">
         <v>1</v>
@@ -19752,7 +19752,7 @@
         <v>45782</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H46" s="7" t="b">
         <v>0</v>
@@ -19785,7 +19785,7 @@
         <v>45803</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H47" s="9" t="b">
         <v>0</v>
@@ -19818,7 +19818,7 @@
         <v>45805</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H48" s="7" t="b">
         <v>0</v>
@@ -19851,7 +19851,7 @@
         <v>45798</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H49" s="9" t="b">
         <v>0</v>

--- a/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
+++ b/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="commsec" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CGT Disposals'!$A$1:$T$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Income'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'⚠ Missing Buys'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resolution Progress'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Positions'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'commsec'!$A$1:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CGT Disposals'!$A$1:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Income'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'⚠ Missing Buys'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resolution Progress'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Positions'!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'commsec'!$A$1:$T$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -81,12 +81,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -152,15 +152,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -174,22 +165,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -198,7 +186,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -579,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -688,142 +676,46 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2022-23</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5411.05</v>
+        <v>101573.7216666667</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4943.95</v>
+        <v>142317.765</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>233.55</v>
+        <v>4757.02</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
+        <v>50258.09</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>233.55</v>
+        <v>4757.02</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>233.55</v>
+        <v>-45501.07</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>233.55</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0</v>
+        <v>1376.2</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>9728.049999999999</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>9285.949999999999</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>680.5</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2024-25</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>3383.55</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>2757.9</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>1116.45</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>625.65</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>625.65</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -844,14 +736,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -863,10 +755,10 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -972,303 +864,1147 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>2022-23</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="n">
-        <v>45068</v>
-      </c>
-      <c r="C2" s="14" t="n">
-        <v>45070</v>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>CBA</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>Commonwealth Bank of Australia</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="n">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>45526</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>45530</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Rio Tinto Limited</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G2" s="13" t="n">
-        <v>108.221</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>98.879</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>5411.05</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>4943.95</v>
-      </c>
-      <c r="K2" s="14" t="n">
-        <v>44630</v>
-      </c>
-      <c r="L2" s="14" t="n">
-        <v>44634</v>
-      </c>
-      <c r="M2" s="13" t="n">
-        <v>438</v>
-      </c>
-      <c r="N2" s="13" t="b">
+      <c r="G2" s="7" t="n">
+        <v>68.9615</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>115.578</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>3448.07</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>5778.9</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>45497</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>45499</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="N2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7" t="n">
+        <v>-2330.82</v>
+      </c>
+      <c r="P2" s="7" t="n">
+        <v>-2330.82</v>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>10015575.0</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>45531</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>45533</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Transurban Group</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>8.784800000000001</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>12.992</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>1756.95</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>2598.4</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>45525</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>45527</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9" t="n">
+        <v>-841.45</v>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>-841.45</v>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R3" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="inlineStr">
+        <is>
+          <t>10016098.0</t>
+        </is>
+      </c>
+      <c r="T3" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n">
+        <v>45553</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>45555</v>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Aristocrat Leisure Limited</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>39.0621</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>20.034</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>19531.05</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>10017</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <v>44822</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>44824</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>731</v>
+      </c>
+      <c r="N4" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="13" t="n">
-        <v>467.1</v>
-      </c>
-      <c r="P2" s="13" t="n">
-        <v>233.55</v>
-      </c>
-      <c r="Q2" s="13" t="inlineStr">
+      <c r="O4" s="11" t="n">
+        <v>9514.049999999999</v>
+      </c>
+      <c r="P4" s="11" t="n">
+        <v>4757.02</v>
+      </c>
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R2" s="13" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S2" s="13" t="inlineStr">
-        <is>
-          <t>10091004.0</t>
-        </is>
-      </c>
-      <c r="T2" s="13" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>45214</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>45216</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="R4" s="11" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>10020605.0</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>45586</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Wesfarmers Limited</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>43.3017</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>75.261</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>2165.08</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>3763.05</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>45516</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>45518</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="N5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>45586</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Wesfarmers Limited</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>43.3017</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>72.893</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2165.08</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>3644.65</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>45555</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>45558</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="N6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>-1479.57</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>-1479.57</v>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>45670</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>45672</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>90.459</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>150.6072</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>4522.95</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>7530.36</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>45590</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>45593</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="N7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>-3007.41</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>-3007.41</v>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>10048091.0</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>45688</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>45691</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>90.877</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>150.6072</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>13631.55</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>22591.09</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>45590</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>45593</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="N8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>10049777.0</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>45691</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>45693</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>189.006</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>303.936</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>37801.2</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>60787.2</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>45489</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>45491</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="N9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>-22986</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>-22986</v>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>45691</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>45693</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>189.006</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>274.642</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>9450.299999999999</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>13732.1</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>45593</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>45595</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="N10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>-4281.8</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>-4281.8</v>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>45712</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>National Australia Bank Limited</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>23.8685</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>40.7903</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>477.37</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>815.8099999999999</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>45572</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>45574</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="N11" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>-338.44</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>-338.44</v>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>10054679.0</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>45733</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>45735</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>11.1053</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>16.2975</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>222.11</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>325.95</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>45558</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>45560</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="N12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>10056525.0</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>45733</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>45735</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>11.1053</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>15.823</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>610.79</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>870.26</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>45706</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>45708</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N13" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>-259.47</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>-259.47</v>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>10056525.0</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>45756</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>45758</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>9.252000000000001</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>15.823</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>45706</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>45708</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>-131.42</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>-131.42</v>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>10061655.0</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>45790</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>45792</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>BHP Group Limited</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>48.6402</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>46.4297</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>9728.049999999999</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>9285.950000000001</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>45080</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>45084</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="N3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="F15" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>44.3313</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>3870</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>6649.7</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>45659</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>45663</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="N15" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>-2779.7</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>-2779.7</v>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>10091002.0</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>10070465.0</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>BHPPAM</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>BHP Put Option Dec-24 $40</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>111.645</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1116.45</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>45545</v>
-      </c>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="N4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>-1116.45</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>-1116.45</v>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>OPTION_CLOSE</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr"/>
-      <c r="T4" s="7" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2024-25</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>45734</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>45735</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>XROCAK</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>XRO Call Option Mar-25 $120</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>676.71</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>328.29</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>3383.55</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1641.45</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>45693</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>OPTION_CLOSE</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>10091010.0</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="B16" s="8" t="n">
+        <v>45799</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>45803</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>86.8085</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>144.8417</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1736.17</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>2896.83</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>45750</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="N16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>-1160.66</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>-1160.66</v>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>10073277.0</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:T16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1279,62 +2015,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Income Type</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -1343,91 +2079,306 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>45211</v>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>45490</v>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
+          <t>WBC</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Westpac Banking Corporation</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Dividend – Westpac Banking Corporation | Franked distribution</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>45496</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>National Australia Bank Limited</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>495</v>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Dividend – National Australia Bank Limited | Franked distribution</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>45575</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
           <t>CSL</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>CSL Limited</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="E4" s="7" t="n">
+        <v>334</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Dividend – CSL Limited | Fully franked | Franking credits: $178.93</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>45379</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Dividend – CSL Limited | Franked distribution</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>45624</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Dividend – CSL Limited | Franked distribution</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>45649</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>WBC</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Westpac Banking Corporation</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Dividend – Westpac Banking Corporation | Franked distribution</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>45705</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>BHP Group Limited</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>263</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E7" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Dividend – BHP Group Limited | Partially franked (70%) | Franking credits: $79.09</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Dividend – BHP Group Limited | Franked distribution</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>45731</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec Cash Account</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Interest Income – CommSec Cash Account | Regular interest payment</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1438,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1452,94 +2403,742 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Qty Unmatched</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Sale Price/Unit ($)</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n">
-        <v>45512</v>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="B2" s="15" t="n">
+        <v>45488</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>26.705</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>10005508.0</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>45518</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>92.14570000000001</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>10012691.0</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>45523</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>TLS</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D4" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E2" s="10" t="n">
-        <v>3.8761</v>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>10091005.0</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="E4" s="4" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>10013474.0</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>45526</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>68.9615</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>10015575.0</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>45545</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>142.6827</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>10019888.0</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>45586</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>43.3017</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>45588</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>71.52670000000001</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>10026882.0</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>45616</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>136.3753</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>10036381.0</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>45646</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>7.7337</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>10039055.0</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>45657</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>20.3911</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>10041921.0</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>45660</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>43.6395</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>10044532.0</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>45667</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>74.2092</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>10046236.0</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>45688</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>90.877</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>10049777.0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>45691</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>189.006</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>45754</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>10060217.0</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>45775</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>WDS</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>15.1395</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>10066199.0</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>45776</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>131.698</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>10067312.0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>45783</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>8.1396</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>10069861.0</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>45790</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>10070465.0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>ACTION REQUIRED: Add missing purchase details to cost_base_history.csv or use the manual entry prompt, then re-run the module.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H20"/>
   <mergeCells count="1">
-    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1551,7 +3150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1565,77 +3164,581 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Sell Date</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Qty Unmatched Before</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Qty Added</t>
         </is>
       </c>
-      <c r="E1" s="21" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>Qty Unmatched After</t>
         </is>
       </c>
-      <c r="F1" s="21" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="21" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Lot IDs Added</t>
         </is>
       </c>
-      <c r="H1" s="21" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr"/>
+      <c r="H2" s="18" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="inlineStr"/>
+      <c r="H3" s="18" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr"/>
+      <c r="H4" s="18" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>350</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr"/>
+      <c r="H5" s="18" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr"/>
+      <c r="H6" s="18" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr"/>
+      <c r="H7" s="18" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="18" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr"/>
+      <c r="H9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr"/>
+      <c r="H11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr"/>
+      <c r="H12" s="18" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr"/>
+      <c r="H13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="18" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>TLS</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="C2" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="22" t="n">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="18" t="n">
         <v>500</v>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr"/>
-      <c r="H2" s="22" t="inlineStr"/>
+      <c r="G15" s="18" t="inlineStr"/>
+      <c r="H15" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>WDS</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr"/>
+      <c r="H16" s="18" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr"/>
+      <c r="H17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr"/>
+      <c r="H19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr"/>
+      <c r="H20" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1646,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1661,47 +3764,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Qty Held</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Cost/Unit ($)</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Total Cost ($)</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="19" t="inlineStr">
         <is>
           <t>Days Held</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="19" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I1" s="19" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
@@ -1710,26 +3813,26 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>WES</t>
+          <t>WBC</t>
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>72.61450000000001</v>
+        <v>30.2287</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>7261.45</v>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>45610</v>
-      </c>
-      <c r="F2" s="16" t="n">
-        <v>45614</v>
+        <v>2267.15</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>45477</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>45481</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>536</v>
+        <v>669</v>
       </c>
       <c r="H2" s="7" t="b">
         <v>1</v>
@@ -1741,33 +3844,33 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>XRO</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>138.7483</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4162.45</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>45664</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>45666</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>482</v>
-      </c>
-      <c r="H3" s="4" t="b">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>WBC</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>28.7355</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>2873.55</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>45509</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>45511</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>637</v>
+      </c>
+      <c r="H3" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -1776,26 +3879,26 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>NAB</t>
+          <t>WBC</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>38.7058</v>
+        <v>27.524</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>9676.450000000001</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>45707</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>45709</v>
+        <v>2752.4</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>45537</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>45539</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>439</v>
+        <v>609</v>
       </c>
       <c r="H4" s="7" t="b">
         <v>1</v>
@@ -1806,8 +3909,437 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>69.45950000000001</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>6945.95</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>45663</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>45665</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>483</v>
+      </c>
+      <c r="H5" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>68.7757</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>10316.35</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>45782</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>45784</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>364</v>
+      </c>
+      <c r="H6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>144.8417</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>7966.29</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>45748</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>45750</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>398</v>
+      </c>
+      <c r="H7" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>4.031</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>201.55</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>45600</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>45602</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>546</v>
+      </c>
+      <c r="H8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>425</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>15.823</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>6724.78</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>45706</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>45708</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>440</v>
+      </c>
+      <c r="H9" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>40.7903</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>5302.74</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>45572</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>45574</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>574</v>
+      </c>
+      <c r="H10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>36.373</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>3637.3</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>45614</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>45616</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>532</v>
+      </c>
+      <c r="H11" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>37.6633</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>7532.65</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>45622</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>45624</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>524</v>
+      </c>
+      <c r="H12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>37.7977</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>5669.65</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>45650</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>45652</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>496</v>
+      </c>
+      <c r="H13" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>CBA</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>157.066</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>3141.32</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>45609</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>45611</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>537</v>
+      </c>
+      <c r="H14" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>31.9747</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2398.1</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>45761</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>45763</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>385</v>
+      </c>
+      <c r="H15" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>30.2399</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>15119.95</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>45769</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>45771</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>377</v>
+      </c>
+      <c r="H16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>WDS</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>23.6763</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1775.73</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>45796</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>45798</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>350</v>
+      </c>
+      <c r="H17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1818,14 +4350,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -1837,109 +4369,109 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>Qty Disposed</t>
         </is>
       </c>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="G1" s="20" t="inlineStr">
         <is>
           <t>Proceeds/Unit ($)</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="H1" s="20" t="inlineStr">
         <is>
           <t>Cost Base/Unit ($)</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="I1" s="20" t="inlineStr">
         <is>
           <t>Total Proceeds ($)</t>
         </is>
       </c>
-      <c r="J1" s="24" t="inlineStr">
+      <c r="J1" s="20" t="inlineStr">
         <is>
           <t>Total Cost Base ($)</t>
         </is>
       </c>
-      <c r="K1" s="24" t="inlineStr">
+      <c r="K1" s="20" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="L1" s="24" t="inlineStr">
+      <c r="L1" s="20" t="inlineStr">
         <is>
           <t>Acq Settlement Date</t>
         </is>
       </c>
-      <c r="M1" s="24" t="inlineStr">
+      <c r="M1" s="20" t="inlineStr">
         <is>
           <t>Held (days)</t>
         </is>
       </c>
-      <c r="N1" s="24" t="inlineStr">
+      <c r="N1" s="20" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="O1" s="24" t="inlineStr">
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>Gross Gain/Loss ($)</t>
         </is>
       </c>
-      <c r="P1" s="24" t="inlineStr">
+      <c r="P1" s="20" t="inlineStr">
         <is>
           <t>Discounted Gain ($)</t>
         </is>
       </c>
-      <c r="Q1" s="24" t="inlineStr">
+      <c r="Q1" s="20" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="R1" s="24" t="inlineStr">
+      <c r="R1" s="20" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="S1" s="24" t="inlineStr">
+      <c r="S1" s="20" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="T1" s="24" t="inlineStr">
+      <c r="T1" s="20" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -1948,57 +4480,57 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>2022-23</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>45068</v>
-      </c>
-      <c r="C2" s="16" t="n">
-        <v>45070</v>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>45526</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>45530</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Commonwealth Bank of Australia</t>
+          <t>Rio Tinto Limited</t>
         </is>
       </c>
       <c r="F2" s="7" t="n">
         <v>50</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>108.221</v>
+        <v>68.9615</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>98.879</v>
+        <v>115.578</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>5411.05</v>
+        <v>3448.07</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>4943.95</v>
-      </c>
-      <c r="K2" s="16" t="n">
-        <v>44630</v>
-      </c>
-      <c r="L2" s="16" t="n">
-        <v>44634</v>
+        <v>5778.9</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>45497</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>45499</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>438</v>
+        <v>29</v>
       </c>
       <c r="N2" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>467.1</v>
+        <v>-2330.82</v>
       </c>
       <c r="P2" s="7" t="n">
-        <v>233.55</v>
+        <v>-2330.82</v>
       </c>
       <c r="Q2" s="7" t="inlineStr">
         <is>
@@ -2012,88 +4544,88 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>10091004.0</t>
+          <t>10015575.0</t>
         </is>
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>45214</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>45216</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>BHP Group Limited</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>45531</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>45533</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Transurban Group</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>48.6402</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>46.4297</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>9728.049999999999</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>9285.950000000001</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>45080</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>45084</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="N3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="G3" s="9" t="n">
+        <v>8.784800000000001</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>12.992</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>1756.95</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>2598.4</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>45525</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>45527</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9" t="n">
+        <v>-841.45</v>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>-841.45</v>
+      </c>
+      <c r="Q3" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>10091002.0</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="R3" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="inlineStr">
+        <is>
+          <t>10016098.0</t>
+        </is>
+      </c>
+      <c r="T3" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
@@ -2103,56 +4635,58 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>45645</v>
+      <c r="B4" s="8" t="n">
+        <v>45553</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>45555</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>BHPPAM</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>BHP Put Option Dec-24 $40</t>
+          <t>Aristocrat Leisure Limited</t>
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0</v>
+        <v>39.0621</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>111.645</v>
+        <v>20.034</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0</v>
+        <v>19531.05</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>1116.45</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>45545</v>
-      </c>
-      <c r="L4" s="7" t="n"/>
+        <v>10017</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>44822</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>44824</v>
+      </c>
       <c r="M4" s="7" t="n">
-        <v>100</v>
+        <v>731</v>
       </c>
       <c r="N4" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>-1116.45</v>
+        <v>9514.049999999999</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>-1116.45</v>
+        <v>4757.02</v>
       </c>
       <c r="Q4" s="7" t="inlineStr">
         <is>
-          <t>OPTION_CLOSE</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="R4" s="7" t="inlineStr">
@@ -2160,89 +4694,931 @@
           <t>commsec</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>10020605.0</t>
+        </is>
+      </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>45734</v>
-      </c>
-      <c r="C5" s="15" t="n">
+      <c r="B5" s="10" t="n">
+        <v>45586</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Wesfarmers Limited</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>43.3017</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>75.261</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>2165.08</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>3763.05</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>45516</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>45518</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="N5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>45586</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Wesfarmers Limited</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>43.3017</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>72.893</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2165.08</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>3644.65</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>45555</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>45558</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="N6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>-1479.57</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>-1479.57</v>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>45670</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>45672</v>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>90.459</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>150.6072</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>4522.95</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>7530.36</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>45590</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>45593</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="N7" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>-3007.41</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>-3007.41</v>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>10048091.0</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>45688</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>45691</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>90.877</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>150.6072</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>13631.55</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>22591.09</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>45590</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>45593</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="N8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>10049777.0</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>45691</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>45693</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>189.006</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>303.936</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>37801.2</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>60787.2</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>45489</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>45491</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="N9" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>-22986</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>-22986</v>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>45691</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>45693</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>189.006</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>274.642</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>9450.299999999999</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>13732.1</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>45593</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>45595</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="N10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>-4281.8</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>-4281.8</v>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>45709</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>45712</v>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>National Australia Bank Limited</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>23.8685</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>40.7903</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>477.37</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>815.8099999999999</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>45572</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>45574</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="N11" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>-338.44</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>-338.44</v>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>10054679.0</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>45733</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>45735</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>XROCAK</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>XRO Call Option Mar-25 $120</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>676.71</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>328.29</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>3383.55</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1641.45</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>45693</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>OPTION_CLOSE</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>10091010.0</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>11.1053</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>16.2975</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>222.11</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>325.95</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>45558</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>45560</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="N12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>10056525.0</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>45733</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>45735</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>11.1053</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>15.823</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>610.79</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>870.26</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>45706</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>45708</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N13" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>-259.47</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>-259.47</v>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>10056525.0</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>45756</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>45758</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>9.252000000000001</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>15.823</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>45706</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>45708</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>-131.42</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>-131.42</v>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>10061655.0</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>45790</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>45792</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>BHP Group Limited</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>44.3313</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>3870</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>6649.7</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>45659</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>45663</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="N15" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>-2779.7</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>-2779.7</v>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>10070465.0</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>45799</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>45803</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>86.8085</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>144.8417</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1736.17</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>2896.83</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>45750</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="N16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>-1160.66</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>-1160.66</v>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>10073277.0</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:T16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
+++ b/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
@@ -13,15 +13,13 @@
     <sheet name="⚠ Missing Buys" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Resolution Progress" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Open Positions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="commsec" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="superhero" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CGT Disposals'!$A$1:$T$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Income'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'⚠ Missing Buys'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resolution Progress'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Positions'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'commsec'!$A$1:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CGT Disposals'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Income'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Positions'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'superhero'!$A$1:$U$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,11 +61,15 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0092400E"/>
-      <sz val="10"/>
+      <color rgb="00065F46"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,37 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00065F46"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0092400E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C3AED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -165,53 +147,27 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -579,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -595,7 +551,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -688,144 +644,48 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2022-23</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>5411.05</v>
+        <v>60493.9</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4943.95</v>
+        <v>42940.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>233.55</v>
+        <v>15752.65</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0</v>
+        <v>370.45</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>233.55</v>
+        <v>2171.6</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>233.55</v>
+        <v>15382.2</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>233.55</v>
+        <v>15382.2</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>commsec</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>9728.049999999999</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>9285.949999999999</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>680.5</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>2024-25</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>3383.55</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>2757.9</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>1116.45</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>625.65</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>625.65</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>commsec</t>
+          <t>superhero</t>
         </is>
       </c>
     </row>
@@ -844,29 +704,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -877,319 +738,343 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Qty Disposed</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Proceeds/Unit ($)</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Cost Base/Unit ($)</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Total Proceeds ($)</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Total Cost Base ($)</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Acq Settlement Date</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Held (days)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Gross Gain/Loss ($)</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Discounted Gain ($)</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>2022-23</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="n">
-        <v>45068</v>
-      </c>
-      <c r="C2" s="14" t="n">
-        <v>45070</v>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>CBA</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>Commonwealth Bank of Australia</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>108.221</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>98.879</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>5411.05</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>4943.95</v>
-      </c>
-      <c r="K2" s="14" t="n">
-        <v>44630</v>
-      </c>
-      <c r="L2" s="14" t="n">
-        <v>44634</v>
-      </c>
-      <c r="M2" s="13" t="n">
-        <v>438</v>
-      </c>
-      <c r="N2" s="13" t="b">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>45552</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>45554</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Aristocrat Leisure Limited</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>52.7303</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>38.2697</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>7909.55</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>5740.45</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>45049</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>45051</v>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>503</v>
+      </c>
+      <c r="O2" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="13" t="n">
-        <v>467.1</v>
-      </c>
-      <c r="P2" s="13" t="n">
-        <v>233.55</v>
-      </c>
-      <c r="Q2" s="13" t="inlineStr">
+      <c r="P2" s="7" t="n">
+        <v>2169.1</v>
+      </c>
+      <c r="Q2" s="7" t="n">
+        <v>1084.55</v>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R2" s="13" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S2" s="13" t="inlineStr">
-        <is>
-          <t>10091004.0</t>
-        </is>
-      </c>
-      <c r="T2" s="13" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
+          <t>SH2401010</t>
+        </is>
+      </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>45214</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>45216</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>45574</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>45576</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>200</v>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Pilbara Minerals Limited</t>
+        </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>48.6402</v>
+        <v>2000</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>46.4297</v>
+        <v>3.1148</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9728.049999999999</v>
+        <v>2.502</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9285.950000000001</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>45080</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>45084</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="N3" s="4" t="b">
+        <v>6229.55</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>5004</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>45574</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>45576</v>
+      </c>
+      <c r="N3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>442.1</v>
+      <c r="O3" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+        <v>1225.55</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1225.55</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>10091002.0</t>
+          <t>superhero</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+          <t>SH2401011</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>BHPPAM</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>BHP Put Option Dec-24 $40</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>45580</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>45581</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>NXTCAK</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>NXT Call Option Oct-24 $18</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="10" t="n">
+        <v>378.955</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>146.045</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>3789.55</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>1460.45</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>45484</v>
+      </c>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="O4" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="7" t="n">
-        <v>111.645</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1116.45</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>45545</v>
-      </c>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="N4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>-1116.45</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>-1116.45</v>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="P4" s="10" t="n">
+        <v>2329.1</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>2329.1</v>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>OPTION_CLOSE</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr"/>
-      <c r="T4" s="7" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>SH2401019</t>
+        </is>
+      </c>
+      <c r="U4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
@@ -1199,76 +1084,480 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>45734</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>45735</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>XROCAK</t>
-        </is>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>45610</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>45614</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>XRO Call Option Mar-25 $120</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>5</v>
+          <t>APT</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Afterpay / Block Inc CDI</t>
+        </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>676.71</v>
+        <v>200</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>328.29</v>
+        <v>107.5477</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3383.55</v>
+        <v>84.15219999999999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1641.45</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>45693</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" s="4" t="b">
+        <v>21509.55</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>16830.45</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>45474</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>45476</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="O5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="O5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
       <c r="P5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
+        <v>4679.1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>4679.1</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>SH2401002</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>45679</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>45681</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Zip Co Limited</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1.2779</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0.8221000000000001</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>6389.55</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>4110.45</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>45493</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>45495</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="O6" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>SH2401004</t>
+        </is>
+      </c>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>45719</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>45721</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>NXT</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NextDC Limited</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>22.0652</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>16.4348</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>6619.55</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>4930.45</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>45509</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>45511</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="O7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1689.1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1689.1</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>SH2401006</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>45744</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>45744</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>ZIPCAK</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>ZIP Call Option Mar-25 $1.50</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>18.5225</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>45663</v>
+      </c>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="O8" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>-370.45</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>-370.45</v>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>OPTION_CLOSE</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>10091010.0</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>45775</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>REA</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>REA Group Limited</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>227.882</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>140.918</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>5697.05</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>3522.95</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>44967</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>44971</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>808</v>
+      </c>
+      <c r="O9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>2174.1</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>1087.05</v>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>SH2401008</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>45796</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>ALLPAM</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>ALL Put Option May-25 $48</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>293.6938</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>121.3063</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>2349.55</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>970.45</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>45708</v>
+      </c>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="O10" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>1379.1</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>1379.1</v>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>OPTION_CLOSE</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>SH2401023</t>
+        </is>
+      </c>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1279,155 +1568,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Income Type</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>45211</v>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>CSL</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>CSL Limited</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>45583</v>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>BHP Group Limited</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Dividend – CSL Limited | Fully franked | Franking credits: $178.93</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>Dividend – BHP Group Limited | Partially franked (70%) | Franking credits: $82.50</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>45379</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>45644</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>263</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+          <t>WDS</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Woodside Energy Group</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Dividend – BHP Group Limited | Partially franked (70%) | Franking credits: $79.09</t>
+          <t>superhero</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+          <t>Dividend – Woodside Energy | MISSING payment details – amount and franking status unknown</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>45646</v>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>CBA</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Commonwealth Bank of Australia</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>490</v>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Dividend – CBA | Fully franked | Franking credits: $210.00</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>45685</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Telstra Group Limited</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Dividend – Telstra Group | Fully franked | Franking credits: $77.14</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>45693</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Mineral Resources Limited</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>DIV</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Dividend – Mineral Resources | MISSING record – dividend amount and franking credits unknown</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:J6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1438,109 +1887,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>FY</t>
-        </is>
-      </c>
-      <c r="B1" s="18" t="inlineStr">
-        <is>
-          <t>Disposal Date</t>
-        </is>
-      </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>Asset Code</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>Qty Unmatched</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>Sale Price/Unit ($)</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="G1" s="18" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H1" s="18" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>2024-25</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="n">
-        <v>45512</v>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>3.8761</v>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>10091005.0</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>ACTION REQUIRED: Add missing purchase details to cost_base_history.csv or use the manual entry prompt, then re-run the module.</t>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>✓ No missing buy transactions detected.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A4:G4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1551,91 +1908,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>Sell Date</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>Qty Unmatched Before</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>Qty Added</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>Qty Unmatched After</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>Lot IDs Added</t>
-        </is>
-      </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>Last Updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
-        <is>
-          <t>TLS</t>
-        </is>
-      </c>
-      <c r="B2" s="22" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="C2" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="22" t="n">
-        <v>500</v>
-      </c>
-      <c r="F2" s="22" t="inlineStr">
-        <is>
-          <t>Unresolved</t>
-        </is>
-      </c>
-      <c r="G2" s="22" t="inlineStr"/>
-      <c r="H2" s="22" t="inlineStr"/>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>No missing buy resolution activity recorded yet.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1646,168 +1929,341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Qty Held</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Cost/Unit ($)</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total Cost ($)</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Days Held</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>WES</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>72.61450000000001</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>7261.45</v>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>45610</v>
-      </c>
-      <c r="F2" s="16" t="n">
-        <v>45614</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>536</v>
-      </c>
-      <c r="H2" s="7" t="b">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>TLS</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1004</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>45512</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>45516</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>634</v>
+      </c>
+      <c r="I2" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
+      <c r="J2" s="10" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>XRO</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2.002</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>4004</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>45574</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>45576</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>572</v>
+      </c>
+      <c r="I3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>WTC</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>138.7483</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4162.45</v>
-      </c>
-      <c r="E3" s="15" t="n">
+      <c r="D4" s="10" t="n">
+        <v>88.7483</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>2662.45</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>45550</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>45552</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>596</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1780.45</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>45664</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="G5" s="9" t="n">
         <v>45666</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>482</v>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="I5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>NAB</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>250</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>38.7058</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>9676.450000000001</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>45707</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>45709</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>439</v>
-      </c>
-      <c r="H4" s="7" t="b">
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>LTR</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1930.45</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>45726</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>45728</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="I6" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>45730</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>45730</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="I7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>PME</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>257.4967</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>3862.45</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>45779</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>45783</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>367</v>
+      </c>
+      <c r="I8" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1818,352 +2274,377 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Qty Disposed</t>
         </is>
       </c>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>Proceeds/Unit ($)</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Cost Base/Unit ($)</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Total Proceeds ($)</t>
         </is>
       </c>
-      <c r="J1" s="24" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Total Cost Base ($)</t>
         </is>
       </c>
-      <c r="K1" s="24" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="L1" s="24" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Acq Settlement Date</t>
         </is>
       </c>
-      <c r="M1" s="24" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Held (days)</t>
         </is>
       </c>
-      <c r="N1" s="24" t="inlineStr">
+      <c r="O1" s="16" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="O1" s="24" t="inlineStr">
+      <c r="P1" s="16" t="inlineStr">
         <is>
           <t>Gross Gain/Loss ($)</t>
         </is>
       </c>
-      <c r="P1" s="24" t="inlineStr">
+      <c r="Q1" s="16" t="inlineStr">
         <is>
           <t>Discounted Gain ($)</t>
         </is>
       </c>
-      <c r="Q1" s="24" t="inlineStr">
+      <c r="R1" s="16" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="R1" s="24" t="inlineStr">
+      <c r="S1" s="16" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="S1" s="24" t="inlineStr">
+      <c r="T1" s="16" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="T1" s="24" t="inlineStr">
+      <c r="U1" s="16" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>2022-23</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>45068</v>
-      </c>
-      <c r="C2" s="16" t="n">
-        <v>45070</v>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>CBA</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Commonwealth Bank of Australia</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>108.221</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>98.879</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>5411.05</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>4943.95</v>
-      </c>
-      <c r="K2" s="16" t="n">
-        <v>44630</v>
-      </c>
-      <c r="L2" s="16" t="n">
-        <v>44634</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>438</v>
-      </c>
-      <c r="N2" s="7" t="b">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>45552</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>45554</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Aristocrat Leisure Limited</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>52.7303</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>38.2697</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>7909.55</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>5740.45</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>45049</v>
+      </c>
+      <c r="M2" s="11" t="n">
+        <v>45051</v>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>503</v>
+      </c>
+      <c r="O2" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="7" t="n">
-        <v>467.1</v>
-      </c>
-      <c r="P2" s="7" t="n">
-        <v>233.55</v>
-      </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="P2" s="10" t="n">
+        <v>2169.1</v>
+      </c>
+      <c r="Q2" s="10" t="n">
+        <v>1084.55</v>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>10091004.0</t>
-        </is>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="inlineStr">
+        <is>
+          <t>SH2401010</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>2023-24</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>45214</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>45216</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>45574</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>45576</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>200</v>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Pilbara Minerals Limited</t>
+        </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>48.6402</v>
+        <v>2000</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>46.4297</v>
+        <v>3.1148</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9728.049999999999</v>
+        <v>2.502</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>9285.950000000001</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>45080</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>45084</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="N3" s="4" t="b">
+        <v>6229.55</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>5004</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>45574</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>45576</v>
+      </c>
+      <c r="N3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="4" t="n">
-        <v>442.1</v>
+      <c r="O3" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>442.1</v>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
+        <v>1225.55</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>1225.55</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>10091002.0</t>
+          <t>superhero</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+          <t>SH2401011</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>45645</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>BHPPAM</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>BHP Put Option Dec-24 $40</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>45580</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>45581</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>NXTCAK</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>NXT Call Option Oct-24 $18</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="10" t="n">
+        <v>378.955</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>146.045</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>3789.55</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>1460.45</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>45484</v>
+      </c>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="O4" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="7" t="n">
-        <v>111.645</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7" t="n">
-        <v>1116.45</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>45545</v>
-      </c>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="N4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>-1116.45</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <v>-1116.45</v>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="P4" s="10" t="n">
+        <v>2329.1</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>2329.1</v>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>OPTION_CLOSE</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr"/>
-      <c r="T4" s="7" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>SH2401019</t>
+        </is>
+      </c>
+      <c r="U4" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
@@ -2173,76 +2654,480 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>45734</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>45735</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>XROCAK</t>
-        </is>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>45610</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>45614</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>XRO Call Option Mar-25 $120</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>5</v>
+          <t>APT</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Afterpay / Block Inc CDI</t>
+        </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>676.71</v>
+        <v>200</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>328.29</v>
+        <v>107.5477</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3383.55</v>
+        <v>84.15219999999999</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1641.45</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>45693</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" s="4" t="b">
+        <v>21509.55</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>16830.45</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>45474</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>45476</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="O5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="O5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
       <c r="P5" s="4" t="n">
-        <v>1742.1</v>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
+        <v>4679.1</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>4679.1</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>SH2401002</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>45679</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>45681</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Zip Co Limited</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>1.2779</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0.8221000000000001</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>6389.55</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>4110.45</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>45493</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>45495</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>186</v>
+      </c>
+      <c r="O6" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>SH2401004</t>
+        </is>
+      </c>
+      <c r="U6" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>45719</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>45721</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>NXT</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NextDC Limited</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>22.0652</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>16.4348</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>6619.55</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>4930.45</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>45509</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>45511</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="O7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1689.1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1689.1</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>SH2401006</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>45744</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>45744</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>ZIPCAK</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>ZIP Call Option Mar-25 $1.50</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>18.5225</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>45663</v>
+      </c>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="O8" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>-370.45</v>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>-370.45</v>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>OPTION_CLOSE</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>10091010.0</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>CommSec_Test_15rows_options.xlsx</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>45775</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>45777</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>REA</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>REA Group Limited</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>227.882</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>140.918</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>5697.05</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>3522.95</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>44967</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>44971</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>808</v>
+      </c>
+      <c r="O9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>2174.1</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1087.05</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>SH2401008</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>45796</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>45797</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>ALLPAM</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>ALL Put Option May-25 $48</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>293.6938</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>121.3063</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>2349.55</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>970.45</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>45708</v>
+      </c>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="O10" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>1379.1</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>1379.1</v>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>OPTION_CLOSE</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>superhero</t>
+        </is>
+      </c>
+      <c r="T10" s="10" t="inlineStr">
+        <is>
+          <t>SH2401023</t>
+        </is>
+      </c>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>Superhero_FY2425.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
+++ b/HSLedger_Trading_Module/output/HSLedger_Equity_CGT_Report.xlsx
@@ -16,12 +16,12 @@
     <sheet name="commsec" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CGT Disposals'!$A$1:$T$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Income'!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'⚠ Missing Buys'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resolution Progress'!$A$1:$H$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Positions'!$A$1:$I$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'commsec'!$A$1:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CGT Disposals'!$A$1:$U$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Income'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'⚠ Missing Buys'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resolution Progress'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Positions'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'commsec'!$A$1:$U$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,7 +67,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -87,11 +87,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -174,32 +169,26 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -680,25 +669,25 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>101573.7216666667</v>
+        <v>82042.67166666666</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>142317.765</v>
+        <v>132300.765</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>4757.02</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>50258.09</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4757.02</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-45501.07</v>
+        <v>-50258.09</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -713,7 +702,7 @@
         <v>1376.2</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -736,29 +725,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -769,95 +759,100 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Qty Disposed</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Proceeds/Unit ($)</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Cost Base/Unit ($)</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Total Proceeds ($)</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Total Cost Base ($)</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Acq Settlement Date</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Held (days)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Gross Gain/Loss ($)</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Discounted Gain ($)</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -869,71 +864,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>45526</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="D2" s="8" t="n">
         <v>45530</v>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>RIO</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Rio Tinto Limited</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="7" t="n">
         <v>68.9615</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="I2" s="7" t="n">
         <v>115.578</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="J2" s="7" t="n">
         <v>3448.07</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="K2" s="7" t="n">
         <v>5778.9</v>
       </c>
-      <c r="K2" s="8" t="n">
+      <c r="L2" s="8" t="n">
         <v>45497</v>
       </c>
-      <c r="L2" s="8" t="n">
+      <c r="M2" s="8" t="n">
         <v>45499</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="N2" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="N2" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <v>-2330.82</v>
+      <c r="O2" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P2" s="7" t="n">
         <v>-2330.82</v>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="n">
+        <v>-2330.82</v>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
           <t>10015575.0</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -945,147 +945,157 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>45531</v>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="D3" s="10" t="n">
         <v>45533</v>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>TCL</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Transurban Group</t>
         </is>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="G3" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="H3" s="9" t="n">
         <v>8.784800000000001</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="I3" s="9" t="n">
         <v>12.992</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="J3" s="9" t="n">
         <v>1756.95</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="K3" s="9" t="n">
         <v>2598.4</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="L3" s="10" t="n">
         <v>45525</v>
       </c>
-      <c r="L3" s="10" t="n">
+      <c r="M3" s="10" t="n">
         <v>45527</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="N3" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="N3" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9" t="n">
-        <v>-841.45</v>
+      <c r="O3" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>-841.45</v>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="9" t="n">
+        <v>-841.45</v>
+      </c>
+      <c r="R3" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S3" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T3" s="9" t="inlineStr">
+        <is>
           <t>10016098.0</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="U3" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
-        <v>45553</v>
-      </c>
-      <c r="C4" s="12" t="n">
-        <v>45555</v>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Aristocrat Leisure Limited</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>39.0621</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>20.034</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>19531.05</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>10017</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>44822</v>
-      </c>
-      <c r="L4" s="12" t="n">
-        <v>44824</v>
-      </c>
-      <c r="M4" s="11" t="n">
-        <v>731</v>
-      </c>
-      <c r="N4" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>9514.049999999999</v>
-      </c>
-      <c r="P4" s="11" t="n">
-        <v>4757.02</v>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>45586</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>45588</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Wesfarmers Limited</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>43.3017</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>75.261</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>2165.08</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>3763.05</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>45516</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>45518</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="O4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>10020605.0</t>
-        </is>
-      </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1097,71 +1107,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>45586</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="D5" s="10" t="n">
         <v>45588</v>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>WES</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Wesfarmers Limited</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="G5" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="H5" s="9" t="n">
         <v>43.3017</v>
       </c>
-      <c r="H5" s="9" t="n">
-        <v>75.261</v>
-      </c>
       <c r="I5" s="9" t="n">
+        <v>72.893</v>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>2165.08</v>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>3763.05</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>45516</v>
+      <c r="K5" s="9" t="n">
+        <v>3644.65</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>45518</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="N5" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>-1597.97</v>
+        <v>45555</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>45558</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="O5" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>-1597.97</v>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
+        <v>-1479.57</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>-1479.57</v>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S5" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
           <t>10025140.0</t>
         </is>
       </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="U5" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1173,71 +1188,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>45586</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>45588</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>WES</t>
-        </is>
+        <v>45670</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>45672</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Wesfarmers Limited</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>43.3017</v>
-      </c>
       <c r="H6" s="7" t="n">
-        <v>72.893</v>
+        <v>90.459</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2165.08</v>
+        <v>150.6072</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>3644.65</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>45555</v>
+        <v>4522.95</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>7530.36</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>45558</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="N6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>-1479.57</v>
+        <v>45590</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>45593</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="O6" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>-1479.57</v>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
+        <v>-3007.41</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>-3007.41</v>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>10025140.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>10048091.0</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1249,71 +1269,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>45670</v>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>45672</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+        <v>45688</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>XRO</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Xero Limited</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
-        <v>50</v>
-      </c>
       <c r="G7" s="9" t="n">
-        <v>90.459</v>
+        <v>150</v>
       </c>
       <c r="H7" s="9" t="n">
+        <v>90.877</v>
+      </c>
+      <c r="I7" s="9" t="n">
         <v>150.6072</v>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>4522.95</v>
-      </c>
       <c r="J7" s="9" t="n">
-        <v>7530.36</v>
-      </c>
-      <c r="K7" s="10" t="n">
+        <v>13631.55</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>22591.09</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>45590</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="M7" s="10" t="n">
         <v>45593</v>
       </c>
-      <c r="M7" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="N7" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>-3007.41</v>
+      <c r="N7" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="O7" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>-3007.41</v>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R7" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S7" s="9" t="inlineStr">
         <is>
-          <t>10048091.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>10049777.0</t>
+        </is>
+      </c>
+      <c r="U7" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1325,71 +1350,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>45688</v>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C8" s="8" t="n">
         <v>45691</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>XRO</t>
-        </is>
+      <c r="D8" s="8" t="n">
+        <v>45693</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Xero Limited</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>150</v>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>90.877</v>
+        <v>200</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>150.6072</v>
+        <v>189.006</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>13631.55</v>
+        <v>303.936</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>22591.09</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>45590</v>
+        <v>37801.2</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>60787.2</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>45593</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="N8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>-8959.540000000001</v>
+        <v>45489</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>45491</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>202</v>
+      </c>
+      <c r="O8" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>-8959.540000000001</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
+        <v>-22986</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>-22986</v>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>10049777.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1401,71 +1431,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>45691</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="D9" s="10" t="n">
         <v>45693</v>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>CSL</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>CSL Limited</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>200</v>
-      </c>
       <c r="G9" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="9" t="n">
         <v>189.006</v>
       </c>
-      <c r="H9" s="9" t="n">
-        <v>303.936</v>
-      </c>
       <c r="I9" s="9" t="n">
-        <v>37801.2</v>
+        <v>274.642</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>60787.2</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>45489</v>
+        <v>9450.299999999999</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>13732.1</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>45491</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="N9" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>-22986</v>
+        <v>45593</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>45595</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="O9" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>-22986</v>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
+        <v>-4281.8</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>-4281.8</v>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S9" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
           <t>10051473.0</t>
         </is>
       </c>
-      <c r="T9" s="9" t="inlineStr">
+      <c r="U9" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1477,71 +1512,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>45691</v>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>45693</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>CSL</t>
-        </is>
+        <v>45709</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>45712</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>CSL Limited</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>50</v>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>National Australia Bank Limited</t>
+        </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>189.006</v>
+        <v>20</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>274.642</v>
+        <v>23.8685</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9450.299999999999</v>
+        <v>40.7903</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>13732.1</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>45593</v>
+        <v>477.37</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>815.8099999999999</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>45595</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="N10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>-4281.8</v>
+        <v>45572</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>45574</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="O10" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>-4281.8</v>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
+        <v>-338.44</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>-338.44</v>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>10051473.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>10054679.0</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1553,71 +1593,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>45709</v>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>45712</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>NAB</t>
-        </is>
+        <v>45733</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>45735</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>National Australia Bank Limited</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n">
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>23.8685</v>
-      </c>
       <c r="H11" s="9" t="n">
-        <v>40.7903</v>
+        <v>11.1053</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>477.37</v>
+        <v>16.2975</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>815.8099999999999</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>45572</v>
+        <v>222.11</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>325.95</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>45574</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>137</v>
-      </c>
-      <c r="N11" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>-338.44</v>
+        <v>45558</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>45560</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="O11" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>-338.44</v>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
+        <v>-103.84</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R11" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S11" s="9" t="inlineStr">
         <is>
-          <t>10054679.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>10056525.0</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1629,71 +1674,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>45733</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="D12" s="8" t="n">
         <v>45735</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>FMG</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Fortescue Ltd</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>20</v>
-      </c>
       <c r="G12" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <v>11.1053</v>
       </c>
-      <c r="H12" s="7" t="n">
-        <v>16.2975</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>222.11</v>
+        <v>15.823</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>325.95</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>45558</v>
+        <v>610.79</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>870.26</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>45560</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="N12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>-103.84</v>
+        <v>45706</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>45708</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O12" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>-103.84</v>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+        <v>-259.47</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>-259.47</v>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
           <t>10056525.0</t>
         </is>
       </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1705,71 +1755,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>45733</v>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>45735</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
+        <v>45756</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>45758</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>FMG</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Fortescue Ltd</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>55</v>
-      </c>
       <c r="G13" s="9" t="n">
-        <v>11.1053</v>
+        <v>20</v>
       </c>
       <c r="H13" s="9" t="n">
+        <v>9.252000000000001</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>15.823</v>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>610.79</v>
-      </c>
       <c r="J13" s="9" t="n">
-        <v>870.26</v>
-      </c>
-      <c r="K13" s="10" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>45706</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="M13" s="10" t="n">
         <v>45708</v>
       </c>
-      <c r="M13" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="N13" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>-259.47</v>
+      <c r="N13" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>-259.47</v>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
+        <v>-131.42</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>-131.42</v>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S13" s="9" t="inlineStr">
         <is>
-          <t>10056525.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>10061655.0</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1781,71 +1836,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>45756</v>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>45758</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>FMG</t>
-        </is>
+        <v>45790</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>45792</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Fortescue Ltd</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>20</v>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>BHP Group Limited</t>
+        </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>9.252000000000001</v>
+        <v>150</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>15.823</v>
+        <v>25.8</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>185.04</v>
+        <v>44.3313</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>316.46</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>45706</v>
+        <v>3870</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>6649.7</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>45708</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="N14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>-131.42</v>
+        <v>45659</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>45663</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="O14" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>-131.42</v>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+        <v>-2779.7</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>-2779.7</v>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>10061655.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>10070465.0</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -1857,154 +1917,83 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>45790</v>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>45792</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
+        <v>45799</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>45803</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>150</v>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
       </c>
       <c r="G15" s="9" t="n">
-        <v>25.8</v>
+        <v>20</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>44.3313</v>
+        <v>86.8085</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>3870</v>
+        <v>144.8417</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6649.7</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>45659</v>
+        <v>1736.17</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>2896.83</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>45663</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>131</v>
-      </c>
-      <c r="N15" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9" t="n">
-        <v>-2779.7</v>
+        <v>45748</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>45750</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="O15" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-2779.7</v>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
+        <v>-1160.66</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>-1160.66</v>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S15" s="9" t="inlineStr">
         <is>
-          <t>10070465.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T15" s="9" t="inlineStr">
         <is>
-          <t>CommSec_Test_FY2024-25.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2024-25</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>45799</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>45803</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>XRO</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Xero Limited</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>86.8085</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>144.8417</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>1736.17</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>2896.83</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>45748</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>45750</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="N16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>-1160.66</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>-1160.66</v>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
           <t>10073277.0</t>
         </is>
       </c>
-      <c r="T16" s="7" t="inlineStr">
+      <c r="U15" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T16"/>
+  <autoFilter ref="A1:U15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2015,62 +2004,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Amount ($)</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Income Type</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -2082,38 +2077,43 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>45490</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>WBC</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Westpac Banking Corporation</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="F2" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
           <t>Dividend – Westpac Banking Corporation | Franked distribution</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -2125,38 +2125,43 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>45496</v>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>NAB</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>National Australia Bank Limited</t>
         </is>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="F3" s="9" t="n">
         <v>495</v>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
           <t>Dividend – National Australia Bank Limited | Franked distribution</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -2168,38 +2173,43 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>45575</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>CSL</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>CSL Limited</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="F4" s="7" t="n">
         <v>334</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
           <t>Dividend – CSL Limited | Franked distribution</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -2211,38 +2221,43 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>45624</v>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>CSL</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>CSL Limited</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="F5" s="9" t="n">
         <v>167</v>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
           <t>Dividend – CSL Limited | Franked distribution</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -2254,38 +2269,43 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>45649</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>WBC</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Westpac Banking Corporation</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
           <t>Dividend – Westpac Banking Corporation | Franked distribution</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -2297,38 +2317,43 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>45705</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>BHP Group Limited</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="F7" s="9" t="n">
         <v>185</v>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>DIV</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
           <t>Dividend – BHP Group Limited | Franked distribution</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -2340,45 +2365,50 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>45731</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>CommSec Cash Account</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="7" t="n">
         <v>45.2</v>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
           <t>Interest Income – CommSec Cash Account | Regular interest payment</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2389,56 +2419,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>Qty Unmatched</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>Sale Price/Unit ($)</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>Action Required</t>
         </is>
@@ -2450,31 +2486,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n">
         <v>45488</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>26.705</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
           <t>10005508.0</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2486,31 +2527,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n">
         <v>45518</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>XRO</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>92.14570000000001</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>10012691.0</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2522,31 +2568,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
         <v>45523</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TLS</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>2.284</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>10013474.0</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2558,31 +2609,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
         <v>45526</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>RIO</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>68.9615</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>10015575.0</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2594,31 +2650,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>45545</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>MQG</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>142.6827</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
           <t>10019888.0</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2630,31 +2691,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>45586</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>WES</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>50</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>45553</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>43.3017</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>39.0621</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>10025140.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>10020605.0</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2666,31 +2732,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
-        <v>45588</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>150</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>45586</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>71.52670000000001</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>43.3017</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>10026882.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2702,31 +2773,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
-        <v>45616</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MQG</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>45588</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>136.3753</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+      <c r="F9" s="4" t="n">
+        <v>71.52670000000001</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>10036381.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>10026882.0</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2738,31 +2814,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n">
-        <v>45646</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>200</v>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>45616</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.7337</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>150</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>136.3753</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>10039055.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>10036381.0</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2774,31 +2855,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
-        <v>45657</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>ANZ</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>500</v>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>45646</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>20.3911</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>200</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>7.7337</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>10041921.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>10039055.0</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2810,31 +2896,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
-        <v>45660</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>WES</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>100</v>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>45657</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>43.6395</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>20.3911</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>10044532.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>10041921.0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2846,31 +2937,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
-        <v>45667</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>RIO</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>200</v>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>45660</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>WES</t>
+        </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>74.2092</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>43.6395</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>10046236.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>10044532.0</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2882,31 +2978,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
-        <v>45688</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>XRO</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>50</v>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>45667</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>RIO</t>
+        </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>90.877</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>200</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>74.2092</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>10049777.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>10046236.0</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2918,31 +3019,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
-        <v>45691</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>CSL</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>250</v>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>45688</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>XRO</t>
+        </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>189.006</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>90.877</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>10051473.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>10049777.0</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2954,31 +3060,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
-        <v>45754</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>ANZ</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>500</v>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>45691</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>CSL</t>
+        </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>250</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>189.006</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>10060217.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -2990,31 +3101,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
-        <v>45775</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>WDS</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>20</v>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>45754</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>15.1395</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>20.44</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>10066199.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>10060217.0</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -3026,31 +3142,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
-        <v>45776</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>MQG</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>50</v>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>45775</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>WDS</t>
+        </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>131.698</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>15.1395</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>10067312.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>10066199.0</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -3062,31 +3183,36 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
-        <v>45783</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>75</v>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>45776</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>MQG</t>
+        </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>8.1396</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>131.698</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>10069861.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>10067312.0</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
@@ -3098,47 +3224,93 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>45783</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>8.1396</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>10069861.0</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
         <v>45790</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>10070465.0</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Provide historical buy details via cost_base_history.csv or manual entry</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ACTION REQUIRED: Add missing purchase details to cost_base_history.csv or use the manual entry prompt, then re-run the module.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:I21"/>
   <mergeCells count="1">
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3150,7 +3322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3164,581 +3336,609 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Sell Date</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Qty Unmatched Before</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Qty Added</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Qty Unmatched After</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Lot IDs Added</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Unresolved</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr"/>
+      <c r="H2" s="16" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>ANZ</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="C2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="18" t="n">
+      <c r="C3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr"/>
-      <c r="H2" s="18" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr"/>
+      <c r="H3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>ANZ</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="18" t="n">
+      <c r="C4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr"/>
-      <c r="H3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="G4" s="16" t="inlineStr"/>
+      <c r="H4" s="16" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>2024-07-15</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="C5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr"/>
-      <c r="H4" s="18" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr"/>
+      <c r="H5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>BHP</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="C6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr"/>
-      <c r="H5" s="18" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr"/>
+      <c r="H6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CSL</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>2025-02-03</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="C7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr"/>
+      <c r="H7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>MQG</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>2024-09-10</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="C8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>MQG</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>2024-11-20</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="C9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr"/>
+      <c r="H9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>MQG</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="18" t="n">
+      <c r="C10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr"/>
+      <c r="H10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>RIO</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>2024-08-22</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="C11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr"/>
+      <c r="H11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>RIO</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>2024-10-23</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="C12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr"/>
+      <c r="H12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>RIO</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>2025-01-10</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="C13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr"/>
-      <c r="H12" s="18" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr"/>
+      <c r="H13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>TCL</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="18" t="n">
+      <c r="C14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="18" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr"/>
+      <c r="H14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>TCL</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="C15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n">
         <v>75</v>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="18" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr"/>
+      <c r="H15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>TLS</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>2024-08-19</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="C16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr"/>
-      <c r="H15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr"/>
+      <c r="H16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>WDS</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>2025-04-28</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="18" t="n">
+      <c r="C17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr"/>
-      <c r="H16" s="18" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr"/>
+      <c r="H17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>WES</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>2024-10-21</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="18" t="n">
+      <c r="C18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr"/>
-      <c r="H17" s="18" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr"/>
+      <c r="H18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>WES</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>2025-01-03</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="18" t="n">
+      <c r="C19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr"/>
-      <c r="H18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr"/>
+      <c r="H19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>XRO</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>2024-08-14</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="18" t="n">
+      <c r="C20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="16" t="n">
         <v>150</v>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr"/>
-      <c r="H19" s="18" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr"/>
+      <c r="H20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>XRO</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="C21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>Unresolved</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr"/>
-      <c r="H20" s="18" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+      <c r="H21" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H20"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3749,62 +3949,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Qty Held</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Cost/Unit ($)</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>Total Cost ($)</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Days Held</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
@@ -3813,31 +4019,36 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
           <t>WBC</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="C2" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="D2" s="7" t="n">
         <v>30.2287</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="E2" s="7" t="n">
         <v>2267.15</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="F2" s="8" t="n">
         <v>45477</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="G2" s="8" t="n">
         <v>45481</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="7" t="n">
         <v>669</v>
       </c>
-      <c r="H2" s="7" t="b">
+      <c r="I2" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -3846,31 +4057,36 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
           <t>WBC</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="C3" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="D3" s="9" t="n">
         <v>28.7355</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="E3" s="9" t="n">
         <v>2873.55</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="F3" s="10" t="n">
         <v>45509</v>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="G3" s="10" t="n">
         <v>45511</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="H3" s="9" t="n">
         <v>637</v>
       </c>
-      <c r="H3" s="9" t="b">
+      <c r="I3" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -3879,31 +4095,36 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
           <t>WBC</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="C4" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="D4" s="7" t="n">
         <v>27.524</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="E4" s="7" t="n">
         <v>2752.4</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="8" t="n">
         <v>45537</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="G4" s="8" t="n">
         <v>45539</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="7" t="n">
         <v>609</v>
       </c>
-      <c r="H4" s="7" t="b">
+      <c r="I4" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -3912,31 +4133,36 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
           <t>WES</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="C5" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="D5" s="9" t="n">
         <v>69.45950000000001</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="E5" s="9" t="n">
         <v>6945.95</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="F5" s="10" t="n">
         <v>45663</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="G5" s="10" t="n">
         <v>45665</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="H5" s="9" t="n">
         <v>483</v>
       </c>
-      <c r="H5" s="9" t="b">
+      <c r="I5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -3945,31 +4171,36 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
           <t>WES</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="C6" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="D6" s="7" t="n">
         <v>68.7757</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>10316.35</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="8" t="n">
         <v>45782</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="G6" s="8" t="n">
         <v>45784</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>364</v>
       </c>
-      <c r="H6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -3978,31 +4209,36 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
           <t>XRO</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="C7" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="D7" s="9" t="n">
         <v>144.8417</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="E7" s="9" t="n">
         <v>7966.29</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="F7" s="10" t="n">
         <v>45748</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="G7" s="10" t="n">
         <v>45750</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>398</v>
       </c>
-      <c r="H7" s="9" t="b">
+      <c r="I7" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4011,31 +4247,36 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
           <t>TLS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="C8" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="D8" s="7" t="n">
         <v>4.031</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="E8" s="7" t="n">
         <v>201.55</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>45600</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="G8" s="8" t="n">
         <v>45602</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>546</v>
       </c>
-      <c r="H8" s="7" t="b">
+      <c r="I8" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4044,31 +4285,36 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
           <t>FMG</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="C9" s="9" t="n">
         <v>425</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="D9" s="9" t="n">
         <v>15.823</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="E9" s="9" t="n">
         <v>6724.78</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="F9" s="10" t="n">
         <v>45706</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="G9" s="10" t="n">
         <v>45708</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="H9" s="9" t="n">
         <v>440</v>
       </c>
-      <c r="H9" s="9" t="b">
+      <c r="I9" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4077,31 +4323,36 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
           <t>NAB</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="C10" s="7" t="n">
         <v>130</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="D10" s="7" t="n">
         <v>40.7903</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>5302.74</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="F10" s="8" t="n">
         <v>45572</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="G10" s="8" t="n">
         <v>45574</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>574</v>
       </c>
-      <c r="H10" s="7" t="b">
+      <c r="I10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4110,31 +4361,36 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
           <t>NAB</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="C11" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="D11" s="9" t="n">
         <v>36.373</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="E11" s="9" t="n">
         <v>3637.3</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="F11" s="10" t="n">
         <v>45614</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="G11" s="10" t="n">
         <v>45616</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="H11" s="9" t="n">
         <v>532</v>
       </c>
-      <c r="H11" s="9" t="b">
+      <c r="I11" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4143,31 +4399,36 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
           <t>NAB</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="C12" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="D12" s="7" t="n">
         <v>37.6633</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="E12" s="7" t="n">
         <v>7532.65</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="F12" s="8" t="n">
         <v>45622</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="G12" s="8" t="n">
         <v>45624</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="H12" s="7" t="n">
         <v>524</v>
       </c>
-      <c r="H12" s="7" t="b">
+      <c r="I12" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4176,31 +4437,36 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
           <t>NAB</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="C13" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="D13" s="9" t="n">
         <v>37.7977</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="E13" s="9" t="n">
         <v>5669.65</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="F13" s="10" t="n">
         <v>45650</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="G13" s="10" t="n">
         <v>45652</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="H13" s="9" t="n">
         <v>496</v>
       </c>
-      <c r="H13" s="9" t="b">
+      <c r="I13" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4209,31 +4475,36 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
           <t>CBA</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="C14" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="D14" s="7" t="n">
         <v>157.066</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="E14" s="7" t="n">
         <v>3141.32</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="F14" s="8" t="n">
         <v>45609</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="G14" s="8" t="n">
         <v>45611</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>537</v>
       </c>
-      <c r="H14" s="7" t="b">
+      <c r="I14" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4242,31 +4513,36 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
           <t>ANZ</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="C15" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="D15" s="9" t="n">
         <v>31.9747</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="E15" s="9" t="n">
         <v>2398.1</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="F15" s="10" t="n">
         <v>45761</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="G15" s="10" t="n">
         <v>45763</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="H15" s="9" t="n">
         <v>385</v>
       </c>
-      <c r="H15" s="9" t="b">
+      <c r="I15" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4275,31 +4551,36 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
           <t>ANZ</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="C16" s="7" t="n">
         <v>500</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="D16" s="7" t="n">
         <v>30.2399</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>15119.95</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="F16" s="8" t="n">
         <v>45769</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="G16" s="8" t="n">
         <v>45771</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="H16" s="7" t="n">
         <v>377</v>
       </c>
-      <c r="H16" s="7" t="b">
+      <c r="I16" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
@@ -4308,38 +4589,43 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
           <t>WDS</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="C17" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="D17" s="9" t="n">
         <v>23.6763</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>1775.73</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="F17" s="10" t="n">
         <v>45796</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="G17" s="10" t="n">
         <v>45798</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="H17" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="H17" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>commsec</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I17"/>
+  <autoFilter ref="A1:J17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4350,128 +4636,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>FY</t>
         </is>
       </c>
-      <c r="B1" s="20" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Disposal Date</t>
         </is>
       </c>
-      <c r="C1" s="20" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Settlement Date</t>
         </is>
       </c>
-      <c r="D1" s="20" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Asset Code</t>
         </is>
       </c>
-      <c r="E1" s="20" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Asset Name</t>
         </is>
       </c>
-      <c r="F1" s="20" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Qty Disposed</t>
         </is>
       </c>
-      <c r="G1" s="20" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>Proceeds/Unit ($)</t>
         </is>
       </c>
-      <c r="H1" s="20" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>Cost Base/Unit ($)</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>Total Proceeds ($)</t>
         </is>
       </c>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>Total Cost Base ($)</t>
         </is>
       </c>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>Acquisition Date</t>
         </is>
       </c>
-      <c r="L1" s="20" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>Acq Settlement Date</t>
         </is>
       </c>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>Held (days)</t>
         </is>
       </c>
-      <c r="N1" s="20" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>Discount Eligible</t>
         </is>
       </c>
-      <c r="O1" s="20" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>Gross Gain/Loss ($)</t>
         </is>
       </c>
-      <c r="P1" s="20" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>Discounted Gain ($)</t>
         </is>
       </c>
-      <c r="Q1" s="20" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="R1" s="20" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
-      <c r="S1" s="20" t="inlineStr">
+      <c r="T1" s="18" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="T1" s="20" t="inlineStr">
+      <c r="U1" s="18" t="inlineStr">
         <is>
           <t>Source File</t>
         </is>
@@ -4483,71 +4775,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>45526</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="D2" s="8" t="n">
         <v>45530</v>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>RIO</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Rio Tinto Limited</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="7" t="n">
         <v>68.9615</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="I2" s="7" t="n">
         <v>115.578</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="J2" s="7" t="n">
         <v>3448.07</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="K2" s="7" t="n">
         <v>5778.9</v>
       </c>
-      <c r="K2" s="8" t="n">
+      <c r="L2" s="8" t="n">
         <v>45497</v>
       </c>
-      <c r="L2" s="8" t="n">
+      <c r="M2" s="8" t="n">
         <v>45499</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="N2" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="N2" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <v>-2330.82</v>
+      <c r="O2" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P2" s="7" t="n">
         <v>-2330.82</v>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="n">
+        <v>-2330.82</v>
+      </c>
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr">
+        <is>
           <t>10015575.0</t>
         </is>
       </c>
-      <c r="T2" s="7" t="inlineStr">
+      <c r="U2" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -4559,71 +4856,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>45531</v>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="D3" s="10" t="n">
         <v>45533</v>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>TCL</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Transurban Group</t>
         </is>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="G3" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="H3" s="9" t="n">
         <v>8.784800000000001</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="I3" s="9" t="n">
         <v>12.992</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="J3" s="9" t="n">
         <v>1756.95</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="K3" s="9" t="n">
         <v>2598.4</v>
       </c>
-      <c r="K3" s="10" t="n">
+      <c r="L3" s="10" t="n">
         <v>45525</v>
       </c>
-      <c r="L3" s="10" t="n">
+      <c r="M3" s="10" t="n">
         <v>45527</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="N3" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="N3" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9" t="n">
-        <v>-841.45</v>
+      <c r="O3" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P3" s="9" t="n">
         <v>-841.45</v>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="Q3" s="9" t="n">
+        <v>-841.45</v>
+      </c>
+      <c r="R3" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R3" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S3" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T3" s="9" t="inlineStr">
+        <is>
           <t>10016098.0</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="U3" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -4635,71 +4937,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>45553</v>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>45555</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
+        <v>45586</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>45588</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Aristocrat Leisure Limited</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>500</v>
+          <t>WES</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Wesfarmers Limited</t>
+        </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>39.0621</v>
+        <v>50</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20.034</v>
+        <v>43.3017</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>19531.05</v>
+        <v>75.261</v>
       </c>
       <c r="J4" s="7" t="n">
-        <v>10017</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>44822</v>
+        <v>2165.08</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>3763.05</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>44824</v>
-      </c>
-      <c r="M4" s="7" t="n">
-        <v>731</v>
-      </c>
-      <c r="N4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>9514.049999999999</v>
+        <v>45516</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>45518</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="O4" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P4" s="7" t="n">
-        <v>4757.02</v>
-      </c>
-      <c r="Q4" s="7" t="inlineStr">
+        <v>-1597.97</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>-1597.97</v>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>10020605.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>10025140.0</t>
+        </is>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -4711,71 +5018,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>45586</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="D5" s="10" t="n">
         <v>45588</v>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>WES</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Wesfarmers Limited</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="G5" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="H5" s="9" t="n">
         <v>43.3017</v>
       </c>
-      <c r="H5" s="9" t="n">
-        <v>75.261</v>
-      </c>
       <c r="I5" s="9" t="n">
+        <v>72.893</v>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>2165.08</v>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>3763.05</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>45516</v>
+      <c r="K5" s="9" t="n">
+        <v>3644.65</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>45518</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="N5" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>-1597.97</v>
+        <v>45555</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>45558</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="O5" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>-1597.97</v>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
+        <v>-1479.57</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>-1479.57</v>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S5" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
           <t>10025140.0</t>
         </is>
       </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="U5" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -4787,71 +5099,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>45586</v>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>45588</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>WES</t>
-        </is>
+        <v>45670</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>45672</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Wesfarmers Limited</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>43.3017</v>
-      </c>
       <c r="H6" s="7" t="n">
-        <v>72.893</v>
+        <v>90.459</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>2165.08</v>
+        <v>150.6072</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>3644.65</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>45555</v>
+        <v>4522.95</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>7530.36</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>45558</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="N6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>-1479.57</v>
+        <v>45590</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>45593</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="O6" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>-1479.57</v>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
+        <v>-3007.41</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>-3007.41</v>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>10025140.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
+        <is>
+          <t>10048091.0</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -4863,71 +5180,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>45670</v>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>45672</v>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+        <v>45688</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>45691</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>XRO</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Xero Limited</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
-        <v>50</v>
-      </c>
       <c r="G7" s="9" t="n">
-        <v>90.459</v>
+        <v>150</v>
       </c>
       <c r="H7" s="9" t="n">
+        <v>90.877</v>
+      </c>
+      <c r="I7" s="9" t="n">
         <v>150.6072</v>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>4522.95</v>
-      </c>
       <c r="J7" s="9" t="n">
-        <v>7530.36</v>
-      </c>
-      <c r="K7" s="10" t="n">
+        <v>13631.55</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>22591.09</v>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>45590</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="M7" s="10" t="n">
         <v>45593</v>
       </c>
-      <c r="M7" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="N7" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>-3007.41</v>
+      <c r="N7" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="O7" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>-3007.41</v>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>-8959.540000000001</v>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R7" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S7" s="9" t="inlineStr">
         <is>
-          <t>10048091.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>10049777.0</t>
+        </is>
+      </c>
+      <c r="U7" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -4939,71 +5261,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>45688</v>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C8" s="8" t="n">
         <v>45691</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>XRO</t>
-        </is>
+      <c r="D8" s="8" t="n">
+        <v>45693</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Xero Limited</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>150</v>
+          <t>CSL</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>CSL Limited</t>
+        </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>90.877</v>
+        <v>200</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>150.6072</v>
+        <v>189.006</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>13631.55</v>
+        <v>303.936</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>22591.09</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>45590</v>
+        <v>37801.2</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>60787.2</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>45593</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="N8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>-8959.540000000001</v>
+        <v>45489</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>45491</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>202</v>
+      </c>
+      <c r="O8" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>-8959.540000000001</v>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
+        <v>-22986</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>-22986</v>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>10049777.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>10051473.0</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5015,71 +5342,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>45691</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="D9" s="10" t="n">
         <v>45693</v>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>CSL</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>CSL Limited</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>200</v>
-      </c>
       <c r="G9" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="9" t="n">
         <v>189.006</v>
       </c>
-      <c r="H9" s="9" t="n">
-        <v>303.936</v>
-      </c>
       <c r="I9" s="9" t="n">
-        <v>37801.2</v>
+        <v>274.642</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>60787.2</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>45489</v>
+        <v>9450.299999999999</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>13732.1</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>45491</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="N9" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>-22986</v>
+        <v>45593</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>45595</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="O9" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>-22986</v>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
+        <v>-4281.8</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>-4281.8</v>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S9" s="9" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
           <t>10051473.0</t>
         </is>
       </c>
-      <c r="T9" s="9" t="inlineStr">
+      <c r="U9" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5091,71 +5423,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>45691</v>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>45693</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>CSL</t>
-        </is>
+        <v>45709</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>45712</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>CSL Limited</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>50</v>
+          <t>NAB</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>National Australia Bank Limited</t>
+        </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>189.006</v>
+        <v>20</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>274.642</v>
+        <v>23.8685</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>9450.299999999999</v>
+        <v>40.7903</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>13732.1</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>45593</v>
+        <v>477.37</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>815.8099999999999</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>45595</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="N10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>-4281.8</v>
+        <v>45572</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>45574</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="O10" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>-4281.8</v>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
+        <v>-338.44</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>-338.44</v>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>10051473.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>10054679.0</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5167,71 +5504,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>45709</v>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>45712</v>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>NAB</t>
-        </is>
+        <v>45733</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>45735</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>National Australia Bank Limited</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n">
+          <t>FMG</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Fortescue Ltd</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>23.8685</v>
-      </c>
       <c r="H11" s="9" t="n">
-        <v>40.7903</v>
+        <v>11.1053</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>477.37</v>
+        <v>16.2975</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>815.8099999999999</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>45572</v>
+        <v>222.11</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>325.95</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>45574</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>137</v>
-      </c>
-      <c r="N11" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>-338.44</v>
+        <v>45558</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>45560</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="O11" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>-338.44</v>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
+        <v>-103.84</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>-103.84</v>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R11" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S11" s="9" t="inlineStr">
         <is>
-          <t>10054679.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>10056525.0</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5243,71 +5585,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>45733</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="D12" s="8" t="n">
         <v>45735</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>FMG</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Fortescue Ltd</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>20</v>
-      </c>
       <c r="G12" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <v>11.1053</v>
       </c>
-      <c r="H12" s="7" t="n">
-        <v>16.2975</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>222.11</v>
+        <v>15.823</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>325.95</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>45558</v>
+        <v>610.79</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>870.26</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>45560</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>175</v>
-      </c>
-      <c r="N12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>-103.84</v>
+        <v>45706</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>45708</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O12" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>-103.84</v>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+        <v>-259.47</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>-259.47</v>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
+          <t>commsec</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
           <t>10056525.0</t>
         </is>
       </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5319,71 +5666,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>45733</v>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>45735</v>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
+        <v>45756</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>45758</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>FMG</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Fortescue Ltd</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>55</v>
-      </c>
       <c r="G13" s="9" t="n">
-        <v>11.1053</v>
+        <v>20</v>
       </c>
       <c r="H13" s="9" t="n">
+        <v>9.252000000000001</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>15.823</v>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>610.79</v>
-      </c>
       <c r="J13" s="9" t="n">
-        <v>870.26</v>
-      </c>
-      <c r="K13" s="10" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>316.46</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>45706</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="M13" s="10" t="n">
         <v>45708</v>
       </c>
-      <c r="M13" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="N13" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>-259.47</v>
+      <c r="N13" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>-259.47</v>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
+        <v>-131.42</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>-131.42</v>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S13" s="9" t="inlineStr">
         <is>
-          <t>10056525.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>10061655.0</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5395,71 +5747,76 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>45756</v>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>45758</v>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>FMG</t>
-        </is>
+        <v>45790</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>45792</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Fortescue Ltd</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>20</v>
+          <t>BHP</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>BHP Group Limited</t>
+        </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>9.252000000000001</v>
+        <v>150</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>15.823</v>
+        <v>25.8</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>185.04</v>
+        <v>44.3313</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>316.46</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>45706</v>
+        <v>3870</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>6649.7</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>45708</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="N14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>-131.42</v>
+        <v>45659</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>45663</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="O14" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>-131.42</v>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+        <v>-2779.7</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>-2779.7</v>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>10061655.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>10070465.0</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
@@ -5471,154 +5828,83 @@
           <t>2024-25</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>45790</v>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>CommSec_Test_FY2024-25.xlsx</t>
+        </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>45792</v>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>BHP</t>
-        </is>
+        <v>45799</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>45803</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>BHP Group Limited</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>150</v>
+          <t>XRO</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Xero Limited</t>
+        </is>
       </c>
       <c r="G15" s="9" t="n">
-        <v>25.8</v>
+        <v>20</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>44.3313</v>
+        <v>86.8085</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>3870</v>
+        <v>144.8417</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6649.7</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>45659</v>
+        <v>1736.17</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>2896.83</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>45663</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>131</v>
-      </c>
-      <c r="N15" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9" t="n">
-        <v>-2779.7</v>
+        <v>45748</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>45750</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="O15" s="9" t="b">
+        <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-2779.7</v>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
+        <v>-1160.66</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>-1160.66</v>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
       <c r="S15" s="9" t="inlineStr">
         <is>
-          <t>10070465.0</t>
+          <t>commsec</t>
         </is>
       </c>
       <c r="T15" s="9" t="inlineStr">
         <is>
-          <t>CommSec_Test_FY2024-25.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2024-25</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>45799</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>45803</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>XRO</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Xero Limited</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>86.8085</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>144.8417</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>1736.17</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>2896.83</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>45748</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>45750</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="N16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>-1160.66</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>-1160.66</v>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>commsec</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
           <t>10073277.0</t>
         </is>
       </c>
-      <c r="T16" s="7" t="inlineStr">
+      <c r="U15" s="9" t="inlineStr">
         <is>
           <t>CommSec_Test_FY2024-25.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T16"/>
+  <autoFilter ref="A1:U15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>